--- a/templates/1.8. Truck _ Template_2026_05_01_BiT.xlsx
+++ b/templates/1.8. Truck _ Template_2026_05_01_BiT.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CONSULTANCY\CMI\analytics-2026\Analysis-Templates\NPN_Water_Template_2026__01_BiT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\CMI-NPN\CMI-DATABASE\Templates-BiT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0DB88C-0191-4CC0-950E-94284079CD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE22DC88-32C7-44ED-BB97-870A6EC577CF}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="1380" windowWidth="20490" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Truck" sheetId="19" r:id="rId1"/>
-    <sheet name="MPDM 1" sheetId="11" r:id="rId2"/>
+    <sheet name="MPDM" sheetId="11" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'MPDM 1'!$A$1:$T$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">MPDM!$A$1:$T$120</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Truck!$A$1:$S$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -573,10 +580,12 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -958,15 +967,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -984,6 +984,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1423,76 +1432,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
     </row>
     <row r="2" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
     </row>
     <row r="3" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
     </row>
     <row r="5" spans="2:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1500,10 +1509,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="11"/>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="53"/>
+      <c r="H6" s="50"/>
       <c r="I6" s="12"/>
       <c r="J6" s="2"/>
       <c r="L6" s="3" t="s">
@@ -1544,12 +1553,12 @@
       <c r="G9" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="47"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="53"/>
       <c r="L9" s="43" t="s">
         <v>2</v>
       </c>
@@ -1624,19 +1633,19 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P11" s="39" t="e">
-        <f>'MPDM 1'!H118*M11</f>
+        <f>MPDM!H118*M11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q11" s="39" t="e">
-        <f>'MPDM 1'!K118*M11</f>
+        <f>MPDM!K118*M11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R11" s="40" t="e">
-        <f>'MPDM 1'!H119</f>
+        <f>MPDM!H119</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S11" s="40" t="e">
-        <f>'MPDM 1'!K119</f>
+        <f>MPDM!K119</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3787,16 +3796,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="G6:H6"/>
     <mergeCell ref="P9:P10"/>
     <mergeCell ref="Q9:Q10"/>
     <mergeCell ref="R9:R10"/>
@@ -3807,6 +3806,16 @@
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="N9:N10"/>
     <mergeCell ref="O9:O10"/>
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3848,75 +3857,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
       <c r="N1" s="13"/>
     </row>
     <row r="2" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
       <c r="N2" s="13"/>
     </row>
     <row r="3" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
       <c r="N3" s="14"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
       <c r="N4" s="14"/>
     </row>
     <row r="5" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -3965,35 +3974,35 @@
       <c r="B11" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="47"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="53"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="21"/>
-      <c r="O11" s="45" t="s">
+      <c r="O11" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="47"/>
-      <c r="V11" s="45" t="s">
+      <c r="P11" s="52"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
+      <c r="T11" s="53"/>
+      <c r="V11" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="W11" s="46"/>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="46"/>
-      <c r="Z11" s="46"/>
-      <c r="AA11" s="47"/>
+      <c r="W11" s="52"/>
+      <c r="X11" s="52"/>
+      <c r="Y11" s="52"/>
+      <c r="Z11" s="52"/>
+      <c r="AA11" s="53"/>
     </row>
     <row r="12" spans="1:27" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="44"/>
@@ -12407,18 +12416,18 @@
     <row r="124" spans="1:21" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="V11:AA11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="O11:T11"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="V11:AA11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="O11:T11"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="18" orientation="portrait" r:id="rId1"/>
